--- a/Faculties/Natural Science/Experimental/Postgrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Experimental/Postgrad Modules Natural Science.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AC076D4-8F5B-4114-977C-6C98B074084E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09881E10-78C0-44E2-94C9-6677A295E75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1383,45 +1383,6 @@
     <t>Master of Clinical Pharmacy 3852</t>
   </si>
   <si>
-    <t>BScHons  Applied Geology  3710</t>
-  </si>
-  <si>
-    <t>BScHons  Astrophysics  3793</t>
-  </si>
-  <si>
-    <t>BScHons  Astrophysics  3793, BScHons  Physical Science  3714</t>
-  </si>
-  <si>
-    <t>BScHons  Biodiversity and Conservation Biology  3731</t>
-  </si>
-  <si>
-    <t>BScHons  Biotechnology  3707</t>
-  </si>
-  <si>
-    <t>BScHons  Biotechnology  3707, BScHons  Medical Bioscience  3721</t>
-  </si>
-  <si>
-    <t>BScHons  Chemistry  3734</t>
-  </si>
-  <si>
-    <t>PGDip  Computer and Media Application  1627</t>
-  </si>
-  <si>
-    <t>BScHons  Statistical Science  3737, BScHons  Computational Finance  3739</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Computational Finance  3739</t>
-  </si>
-  <si>
-    <t>BScHons  Computational Finance  3739, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
-    <t>BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Computer Science  3735, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
     <t xml:space="preserve">Computer Science 737  Artificial Intelligence </t>
   </si>
   <si>
@@ -1443,78 +1404,15 @@
     <t xml:space="preserve">Computer Science 743  Adv Immersive Tech </t>
   </si>
   <si>
-    <t>BScHons  Environment and Water Science  3780</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Computational Finance  3739, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Medical Bioscience  3721</t>
-  </si>
-  <si>
-    <t>BScHons  Physical Science  3714</t>
-  </si>
-  <si>
-    <t>BScHons  Physical Science  3714, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Population Studies  3738</t>
-  </si>
-  <si>
-    <t>BScHons  Population Studies  3738, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
     <t>Research Project  Population Studies  761</t>
   </si>
   <si>
-    <t>BScHons  Population Studies  3738, BScHons  Medical Bioscience  3721</t>
-  </si>
-  <si>
-    <t>BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
     <t xml:space="preserve">STA331, STA332,  STA739 </t>
   </si>
   <si>
-    <t>BScHons  Computational Finance  3739</t>
-  </si>
-  <si>
-    <t>BScHons  Statistical Science  3737, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>PGDip  IWRM  3880</t>
-  </si>
-  <si>
     <t>Mini-Thesis  Research Project  803</t>
   </si>
   <si>
-    <t>MSc  Mathematical Science  3849</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MSc  Computational Finance  3093</t>
-  </si>
-  <si>
-    <t>MSc  Computational Finance  3093</t>
-  </si>
-  <si>
-    <t>MPhil  Population Studies  3921, MSc  Statistical Science  3838, MSc  Computational Finance  3093</t>
-  </si>
-  <si>
-    <t>MSc  Computational Finance  3093, MSc  Statistical Science  3838</t>
-  </si>
-  <si>
-    <t>MSc  Nanoscience  3089</t>
-  </si>
-  <si>
     <t>Foundations of Nanobiomedical Science  Non-Bio  813</t>
   </si>
   <si>
@@ -1524,34 +1422,136 @@
     <t>Foundations of Nanophysics  Non-Phys  833</t>
   </si>
   <si>
-    <t>MSc  Pharmacy Admin and Policy Regulation  3859</t>
-  </si>
-  <si>
     <t>Pharmaceutical Care – Adult Medicine  1  815</t>
   </si>
   <si>
     <t>Pharmaceutical Care - Adult Medicine  2  820</t>
   </si>
   <si>
-    <t>MSc  Physical Science  3081</t>
-  </si>
-  <si>
-    <t>MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MSc  Computational Finance  3093, MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MSc  Medical Biosciences  3819, MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Sciences  3838</t>
+    <t>BScHons Applied Geology 3710</t>
+  </si>
+  <si>
+    <t>BScHons Astrophysics 3793</t>
+  </si>
+  <si>
+    <t>BScHons Astrophysics 3793, BScHons Physical Science 3714</t>
+  </si>
+  <si>
+    <t>BScHons Biodiversity and Conservation Biology 3731</t>
+  </si>
+  <si>
+    <t>BScHons Biotechnology 3707</t>
+  </si>
+  <si>
+    <t>BScHons Biotechnology 3707, BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Chemistry 3734</t>
+  </si>
+  <si>
+    <t>PGDip Computer and Media Application 1627</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737, BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Computational Finance 3739, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Computer Science 3735, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Environment and Water Science 3780</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Physical Science 3714</t>
+  </si>
+  <si>
+    <t>BScHons Physical Science 3714, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738, BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>PGDip IWRM 3880</t>
+  </si>
+  <si>
+    <t>MSc Mathematical Science 3849</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MPhil Population Studies 3921, MSc Statistical Science 3838, MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MSc Computational Finance 3093, MSc Statistical Science 3838</t>
+  </si>
+  <si>
+    <t>MSc Nanoscience 3089</t>
+  </si>
+  <si>
+    <t>MSc Pharmacy Admin and Policy Regulation 3859</t>
+  </si>
+  <si>
+    <t>MSc Physical Science 3081</t>
+  </si>
+  <si>
+    <t>MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Computational Finance 3093, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Medical Biosciences 3819, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Sciences 3838</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1943,7 +1943,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
@@ -1963,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
@@ -1983,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
@@ -1992,7 +1992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
@@ -2023,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
@@ -2043,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -2052,7 +2052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
@@ -2103,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
@@ -2112,7 +2112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>8</v>
@@ -2172,7 +2172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>8</v>
@@ -2212,7 +2212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>8</v>
@@ -2252,7 +2252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
@@ -2272,7 +2272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
@@ -2292,7 +2292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>8</v>
@@ -2312,7 +2312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>8</v>
@@ -2352,7 +2352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
@@ -2372,7 +2372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>8</v>
@@ -2392,7 +2392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>56</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>8</v>
@@ -2432,7 +2432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>60</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>8</v>
@@ -2452,7 +2452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>62</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>8</v>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>66</v>
@@ -2492,7 +2492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>67</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>8</v>
@@ -2512,7 +2512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>69</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
@@ -2543,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
@@ -2552,7 +2552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>73</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
@@ -2572,7 +2572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>75</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>8</v>
@@ -2592,7 +2592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>77</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>8</v>
@@ -2612,7 +2612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>79</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>8</v>
@@ -2643,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>8</v>
@@ -2663,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>8</v>
@@ -2703,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>8</v>
@@ -2723,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>8</v>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>8</v>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>8</v>
@@ -2812,7 +2812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>99</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>46024</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>101</v>
@@ -2832,7 +2832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>102</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>104</v>
@@ -2852,7 +2852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>105</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>107</v>
@@ -2872,7 +2872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>108</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>110</v>
@@ -2892,7 +2892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>111</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>8</v>
@@ -2912,7 +2912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>113</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
@@ -2932,7 +2932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>115</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>110</v>
@@ -2952,7 +2952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>117</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>119</v>
@@ -2983,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>8</v>
@@ -3003,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>8</v>
@@ -3012,7 +3012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>124</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
@@ -3043,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
@@ -3052,7 +3052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>128</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
@@ -3072,18 +3072,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C60" s="1">
         <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
@@ -3097,13 +3097,13 @@
         <v>131</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="C61" s="1">
         <v>1</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
@@ -3117,13 +3117,13 @@
         <v>132</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="C62" s="1">
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>8</v>
@@ -3137,13 +3137,13 @@
         <v>133</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C63" s="1">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
@@ -3157,13 +3157,13 @@
         <v>134</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="C64" s="1">
         <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>135</v>
@@ -3177,13 +3177,13 @@
         <v>136</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="C65" s="1">
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
@@ -3197,13 +3197,13 @@
         <v>137</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="C66" s="1">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>8</v>
@@ -3223,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>8</v>
@@ -3252,7 +3252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>142</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>8</v>
@@ -3272,7 +3272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>144</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -3292,7 +3292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>146</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -3312,7 +3312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>148</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>8</v>
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>152</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>8</v>
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>154</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>8</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>8</v>
@@ -3412,7 +3412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>158</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>8</v>
@@ -3432,7 +3432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>160</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
@@ -3452,7 +3452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>162</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
@@ -3483,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>8</v>
@@ -3492,7 +3492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>166</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>8</v>
@@ -3523,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
@@ -3532,7 +3532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>170</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>8</v>
@@ -3552,7 +3552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>172</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>174</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>8</v>
@@ -3592,7 +3592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>176</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
@@ -3612,7 +3612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>178</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
@@ -3632,7 +3632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>180</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>8</v>
@@ -3663,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
@@ -3683,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
@@ -3692,7 +3692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>186</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>8</v>
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>8</v>
@@ -3763,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>8</v>
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>8</v>
@@ -3803,7 +3803,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>8</v>
@@ -3812,7 +3812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>198</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
@@ -3843,7 +3843,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>8</v>
@@ -3863,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>8</v>
@@ -3872,7 +3872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>204</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>8</v>
@@ -3892,7 +3892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>206</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
@@ -3912,7 +3912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>208</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>8</v>
@@ -3932,7 +3932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>8</v>
@@ -3952,7 +3952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>212</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>8</v>
@@ -4003,7 +4003,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>214</v>
@@ -4012,7 +4012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>218</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>214</v>
@@ -4032,7 +4032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>220</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>8</v>
@@ -4052,7 +4052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>222</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
@@ -4072,7 +4072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>224</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
@@ -4103,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>228</v>
@@ -4112,7 +4112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>229</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>228</v>
@@ -4132,7 +4132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>231</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>233</v>
@@ -4152,18 +4152,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>234</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>8</v>
@@ -4172,7 +4172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>235</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>8</v>
@@ -4192,7 +4192,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>237</v>
       </c>
@@ -4203,16 +4203,16 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>239</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>241</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>243</v>
@@ -4252,7 +4252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>244</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>246</v>
@@ -4272,7 +4272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>247</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>246</v>
@@ -4292,7 +4292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>249</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>251</v>
@@ -4312,7 +4312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>252</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>8</v>
@@ -4332,7 +4332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>254</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>8</v>
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -4372,7 +4372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>258</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>246</v>
@@ -4392,7 +4392,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>260</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>8</v>
@@ -4412,7 +4412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>262</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>228</v>
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>8</v>
@@ -4463,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>8</v>
@@ -4483,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>8</v>
@@ -4523,7 +4523,7 @@
         <v>1</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>8</v>
@@ -4543,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>8</v>
@@ -4563,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>8</v>
@@ -4583,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>8</v>
@@ -4597,13 +4597,13 @@
         <v>280</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>489</v>
+        <v>461</v>
       </c>
       <c r="C136" s="1">
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>46024</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>8</v>
@@ -4643,7 +4643,7 @@
         <v>46024</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>8</v>
@@ -4652,7 +4652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>285</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>46024</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>8</v>
@@ -4683,7 +4683,7 @@
         <v>46024</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
@@ -4703,7 +4703,7 @@
         <v>46024</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>8</v>
@@ -4723,7 +4723,7 @@
         <v>46024</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>8</v>
@@ -4743,7 +4743,7 @@
         <v>46024</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>46024</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>8</v>
@@ -4783,7 +4783,7 @@
         <v>46024</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>8</v>
@@ -4803,7 +4803,7 @@
         <v>46024</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>8</v>
@@ -4823,7 +4823,7 @@
         <v>46024</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>8</v>
@@ -4843,7 +4843,7 @@
         <v>46024</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -4852,7 +4852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>305</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>46024</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>107</v>
@@ -4872,7 +4872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>307</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>46024</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>8</v>
@@ -4892,7 +4892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>309</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>46024</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>110</v>
@@ -4912,7 +4912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>311</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>46024</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>104</v>
@@ -4932,7 +4932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>313</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>46024</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>110</v>
@@ -4952,7 +4952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>315</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>46024</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>110</v>
@@ -4972,7 +4972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>317</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>46024</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>107</v>
@@ -4992,7 +4992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>319</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>46024</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>321</v>
@@ -5012,7 +5012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>322</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>46024</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>110</v>
@@ -5032,7 +5032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>324</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>46024</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>110</v>
@@ -5063,7 +5063,7 @@
         <v>46024</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -5083,7 +5083,7 @@
         <v>46024</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>8</v>
@@ -5103,7 +5103,7 @@
         <v>46024</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>8</v>
@@ -5123,7 +5123,7 @@
         <v>46024</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
@@ -5143,7 +5143,7 @@
         <v>46024</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>8</v>
@@ -5157,13 +5157,13 @@
         <v>336</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="C164" s="3">
         <v>46024</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>8</v>
@@ -5183,7 +5183,7 @@
         <v>46024</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>339</v>
@@ -5203,7 +5203,7 @@
         <v>46024</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>342</v>
@@ -5217,13 +5217,13 @@
         <v>343</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="C167" s="3">
         <v>46024</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>8</v>
@@ -5232,7 +5232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>344</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>46024</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>46024</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>346</v>
@@ -5277,13 +5277,13 @@
         <v>349</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="C170" s="3">
         <v>46024</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>8</v>
@@ -5292,7 +5292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>350</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>46024</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>8</v>
@@ -5312,7 +5312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>352</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>46024</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>8</v>
@@ -5332,7 +5332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>354</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>46024</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>8</v>
@@ -5352,7 +5352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>356</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>46024</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>8</v>
@@ -5372,7 +5372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>358</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>46024</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>8</v>
@@ -5392,7 +5392,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>360</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>46024</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>8</v>
@@ -5412,7 +5412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>362</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>46024</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>8</v>
@@ -5432,7 +5432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>364</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>46024</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>8</v>
@@ -5452,7 +5452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>366</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>46024</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5472,7 +5472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>368</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>46024</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>8</v>
@@ -5492,7 +5492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>370</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>46024</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>8</v>
@@ -5512,7 +5512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>372</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>46024</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>381</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>383</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="C187" s="3">
         <v>46024</v>
@@ -5657,7 +5657,7 @@
         <v>387</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="C189" s="3">
         <v>46024</v>
@@ -5732,7 +5732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>394</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>396</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>400</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>404</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>406</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>408</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>410</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>413</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>415</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>422</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>424</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>46024</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>426</v>
@@ -6032,7 +6032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>427</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>429</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>431</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>434</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>436</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>438</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>440</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>443</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>449</v>
       </c>
